--- a/unduhan/latihan-02-stok-gudang-kunci.xlsx
+++ b/unduhan/latihan-02-stok-gudang-kunci.xlsx
@@ -27,7 +27,7 @@
     <t xml:space="preserve">Kunci Jawaban: Stok Gudang Alat Tulis dan Perlengkapan Kantor</t>
   </si>
   <si>
-    <t xml:space="preserve">Latihan 2 dari 24  |  Tingkat: Pemula  |  Perkiraan waktu: 40 menit  |  pushexcel.github.io/Pushexcel</t>
+    <t xml:space="preserve">Latihan 2 dari 104  |  Tingkat: Pemula  |  Perkiraan waktu: 40 menit  |  pushexcel.github.io/Pushexcel</t>
   </si>
   <si>
     <t xml:space="preserve">Skenario</t>
